--- a/data/GPS/Metricas_GPS8.xlsx
+++ b/data/GPS/Metricas_GPS8.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_02943581D5350E96AE5CCE1F5DBD5F0FE97B260F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8266920C-25D1-46B1-836D-4D8A64941F97}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Fecha</t>
   </si>
@@ -93,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jorge_vicaria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Garcia_Gumiel </t>
   </si>
   <si>
     <t xml:space="preserve">Gonzalo_Echavarria </t>
@@ -131,25 +137,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -160,41 +167,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -202,7 +211,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -392,22 +401,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -416,21 +428,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,12 +490,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="1">
-        <v>83.917</v>
+        <v>83.917000000000002</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -491,45 +504,45 @@
         <v>19</v>
       </c>
       <c r="E2" s="1">
-        <v>5.932</v>
+        <v>5.9320000000000004</v>
       </c>
       <c r="F2" s="1">
         <v>0.628</v>
       </c>
       <c r="G2" s="1">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="H2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1">
-        <v>4.612</v>
+        <v>4.6120000000000001</v>
       </c>
       <c r="M2" s="1">
-        <v>-5.418</v>
+        <v>-5.4180000000000001</v>
       </c>
       <c r="N2" s="1">
-        <v>28.217</v>
+        <v>28.216999999999999</v>
       </c>
       <c r="O2" s="1">
         <v>1179.415</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B3" s="1">
-        <v>80.9</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -538,45 +551,45 @@
         <v>21</v>
       </c>
       <c r="E3" s="1">
-        <v>5.576</v>
+        <v>5.5759999999999996</v>
       </c>
       <c r="F3" s="1">
-        <v>0.356</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="G3" s="1">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="L3" s="1">
-        <v>4.668</v>
+        <v>4.6680000000000001</v>
       </c>
       <c r="M3" s="1">
-        <v>-4.688</v>
+        <v>-4.6879999999999997</v>
       </c>
       <c r="N3" s="1">
-        <v>27.824</v>
+        <v>27.824000000000002</v>
       </c>
       <c r="O3" s="1">
-        <v>1194.167</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>1194.1669999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B4" s="1">
-        <v>77.833</v>
+        <v>77.832999999999998</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -585,45 +598,45 @@
         <v>23</v>
       </c>
       <c r="E4" s="1">
-        <v>4.938</v>
+        <v>4.9379999999999997</v>
       </c>
       <c r="F4" s="1">
-        <v>0.446</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="G4" s="1">
-        <v>0.065</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K4" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L4" s="1">
-        <v>4.398</v>
+        <v>4.3979999999999997</v>
       </c>
       <c r="M4" s="1">
-        <v>-4.735</v>
+        <v>-4.7350000000000003</v>
       </c>
       <c r="N4" s="1">
-        <v>28.037</v>
+        <v>28.036999999999999</v>
       </c>
       <c r="O4" s="1">
-        <v>830.248</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>830.24800000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B5" s="1">
-        <v>81.433</v>
+        <v>81.433000000000007</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
@@ -632,42 +645,42 @@
         <v>21</v>
       </c>
       <c r="E5" s="1">
-        <v>5.654</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F5" s="1">
-        <v>0.233</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="G5" s="1">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="H5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="K5" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L5" s="1">
-        <v>4.174</v>
+        <v>4.1740000000000004</v>
       </c>
       <c r="M5" s="1">
-        <v>-4.199</v>
+        <v>-4.1989999999999998</v>
       </c>
       <c r="N5" s="1">
         <v>25.747</v>
       </c>
       <c r="O5" s="1">
-        <v>865.934</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>865.93399999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B6" s="1">
         <v>80.25</v>
@@ -682,39 +695,39 @@
         <v>4.05</v>
       </c>
       <c r="F6" s="1">
-        <v>0.387</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K6" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="L6" s="1">
-        <v>4.788</v>
+        <v>4.7880000000000003</v>
       </c>
       <c r="M6" s="1">
-        <v>-5.621</v>
+        <v>-5.6210000000000004</v>
       </c>
       <c r="N6" s="1">
-        <v>28.732</v>
+        <v>28.731999999999999</v>
       </c>
       <c r="O6" s="1">
-        <v>988.569</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>988.56899999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B7" s="1">
         <v>80.7</v>
@@ -726,7 +739,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="1">
-        <v>5.832</v>
+        <v>5.8319999999999999</v>
       </c>
       <c r="F7" s="1">
         <v>0.435</v>
@@ -735,407 +748,360 @@
         <v>0.03</v>
       </c>
       <c r="H7" s="1">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I7" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="1">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="K7" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="L7" s="1">
         <v>4.367</v>
       </c>
       <c r="M7" s="1">
-        <v>-4.672</v>
+        <v>-4.6719999999999997</v>
       </c>
       <c r="N7" s="1">
         <v>30.262</v>
       </c>
       <c r="O7" s="1">
-        <v>1195.138</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1195.1379999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B8" s="1">
-        <v>79.967</v>
+        <v>84.117000000000004</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1">
-        <v>5.736</v>
+        <v>5.8630000000000004</v>
       </c>
       <c r="F8" s="1">
-        <v>0.337</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="G8" s="1">
-        <v>0.007</v>
+        <v>0.152</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="I8" s="1">
-        <v>1.0</v>
+        <v>10</v>
       </c>
       <c r="J8" s="1">
-        <v>37.0</v>
+        <v>35</v>
       </c>
       <c r="K8" s="1">
-        <v>23.0</v>
+        <v>44</v>
       </c>
       <c r="L8" s="1">
-        <v>4.46</v>
+        <v>4.8280000000000003</v>
       </c>
       <c r="M8" s="1">
-        <v>-5.977</v>
+        <v>-5.8</v>
       </c>
       <c r="N8" s="1">
-        <v>28.188</v>
+        <v>33.444000000000003</v>
       </c>
       <c r="O8" s="1">
-        <v>1228.622</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>888.87900000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B9" s="1">
-        <v>84.117</v>
+        <v>79.867000000000004</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1">
-        <v>5.863</v>
+        <v>5.6719999999999997</v>
       </c>
       <c r="F9" s="1">
-        <v>0.761</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="G9" s="1">
-        <v>0.152</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H9" s="1">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>10.0</v>
+        <v>5</v>
       </c>
       <c r="J9" s="1">
-        <v>35.0</v>
+        <v>45</v>
       </c>
       <c r="K9" s="1">
-        <v>44.0</v>
+        <v>35</v>
       </c>
       <c r="L9" s="1">
-        <v>4.828</v>
+        <v>4.7679999999999998</v>
       </c>
       <c r="M9" s="1">
-        <v>-5.8</v>
+        <v>-5.2590000000000003</v>
       </c>
       <c r="N9" s="1">
-        <v>33.444</v>
+        <v>28.721</v>
       </c>
       <c r="O9" s="1">
-        <v>888.879</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1133.1769999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B10" s="1">
-        <v>79.867</v>
+        <v>83.533000000000001</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1">
-        <v>5.672</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="F10" s="1">
-        <v>0.642</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="G10" s="1">
-        <v>0.045</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>0.0</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I10" s="1">
-        <v>5.0</v>
+        <v>14</v>
       </c>
       <c r="J10" s="1">
-        <v>45.0</v>
+        <v>28</v>
       </c>
       <c r="K10" s="1">
-        <v>35.0</v>
+        <v>37</v>
       </c>
       <c r="L10" s="1">
-        <v>4.768</v>
+        <v>4.6609999999999996</v>
       </c>
       <c r="M10" s="1">
-        <v>-5.259</v>
+        <v>-8.2059999999999995</v>
       </c>
       <c r="N10" s="1">
-        <v>28.721</v>
+        <v>32.029000000000003</v>
       </c>
       <c r="O10" s="1">
-        <v>1133.177</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1142.1579999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B11" s="1">
-        <v>83.533</v>
+        <v>86.417000000000002</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>6.667</v>
+        <v>3.7850000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>1.09</v>
+        <v>0.23</v>
       </c>
       <c r="G11" s="1">
-        <v>0.177</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="H11" s="1">
-        <v>0.035</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="I11" s="1">
-        <v>14.0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1">
-        <v>28.0</v>
+        <v>19</v>
       </c>
       <c r="K11" s="1">
-        <v>37.0</v>
+        <v>16</v>
       </c>
       <c r="L11" s="1">
-        <v>4.661</v>
+        <v>5.6929999999999996</v>
       </c>
       <c r="M11" s="1">
-        <v>-8.206</v>
+        <v>-4.1630000000000003</v>
       </c>
       <c r="N11" s="1">
-        <v>32.029</v>
+        <v>32.249000000000002</v>
       </c>
       <c r="O11" s="1">
-        <v>1142.158</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>652.11199999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B12" s="1">
-        <v>86.417</v>
+        <v>80.516999999999996</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E12" s="1">
-        <v>3.785</v>
+        <v>5.17</v>
       </c>
       <c r="F12" s="1">
         <v>0.23</v>
       </c>
       <c r="G12" s="1">
-        <v>0.064</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H12" s="1">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>3.0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="1">
-        <v>19.0</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1">
-        <v>16.0</v>
+        <v>24</v>
       </c>
       <c r="L12" s="1">
-        <v>5.693</v>
+        <v>4.4370000000000003</v>
       </c>
       <c r="M12" s="1">
-        <v>-4.163</v>
+        <v>-5.3650000000000002</v>
       </c>
       <c r="N12" s="1">
-        <v>32.249</v>
+        <v>25.459</v>
       </c>
       <c r="O12" s="1">
-        <v>652.112</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>828.649</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46260.0</v>
+        <v>46260</v>
       </c>
       <c r="B13" s="1">
-        <v>80.517</v>
+        <v>80.683000000000007</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1">
+        <v>5.8159999999999998</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9</v>
+      </c>
+      <c r="J13" s="1">
+        <v>101</v>
+      </c>
+      <c r="K13" s="1">
+        <v>59</v>
+      </c>
+      <c r="L13" s="1">
+        <v>8.6709999999999994</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-10.211</v>
+      </c>
+      <c r="N13" s="1">
+        <v>32.104999999999997</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1593.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="1">
+        <v>81.033000000000001</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="1">
+        <v>6.2640000000000002</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.879</v>
+      </c>
+      <c r="G14" s="1">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>7</v>
+      </c>
+      <c r="J14" s="1">
         <v>34</v>
       </c>
-      <c r="E13" s="1">
-        <v>5.17</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.003</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>4.437</v>
-      </c>
-      <c r="M13" s="1">
-        <v>-5.365</v>
-      </c>
-      <c r="N13" s="1">
-        <v>25.459</v>
-      </c>
-      <c r="O13" s="1">
-        <v>828.649</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>46260.0</v>
-      </c>
-      <c r="B14" s="1">
-        <v>80.683</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="1">
-        <v>5.816</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0.603</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.101</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0.034</v>
-      </c>
-      <c r="I14" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>101.0</v>
-      </c>
       <c r="K14" s="1">
-        <v>59.0</v>
+        <v>42</v>
       </c>
       <c r="L14" s="1">
-        <v>8.671</v>
+        <v>4.8689999999999998</v>
       </c>
       <c r="M14" s="1">
-        <v>-10.211</v>
+        <v>-6.5750000000000002</v>
       </c>
       <c r="N14" s="1">
-        <v>32.105</v>
+        <v>28.663</v>
       </c>
       <c r="O14" s="1">
-        <v>1593.39</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>46260.0</v>
-      </c>
-      <c r="B15" s="1">
-        <v>81.033</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="1">
-        <v>6.264</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.879</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.083</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>4.869</v>
-      </c>
-      <c r="M15" s="1">
-        <v>-6.575</v>
-      </c>
-      <c r="N15" s="1">
-        <v>28.663</v>
-      </c>
-      <c r="O15" s="1">
         <v>1286.664</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>